--- a/config/data/WaveSlot.xlsx
+++ b/config/data/WaveSlot.xlsx
@@ -1,130 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WaveSlot" sheetId="1" r:id="rId1"/>
+    <sheet name="WaveSlot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>WaveSlot</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>89dc30e3a2754d22</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>wave_id</t>
-  </si>
-  <si>
-    <t>spawn_sequence</t>
-  </si>
-  <si>
-    <t>formation_index</t>
-  </si>
-  <si>
-    <t>enemy_variant_id</t>
-  </si>
-  <si>
-    <t>level_override</t>
-  </si>
-  <si>
-    <t>initial_phase_id</t>
-  </si>
-  <si>
-    <t>required_for_victory</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EncounterWave.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;i32&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;ref&lt;EnemyPhase.id&gt;&gt;</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..32</t>
-  </si>
-  <si>
-    <t>range=0..31</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -437,160 +407,882 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>WaveSlot</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>89dc30e3a2754d22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>wave_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>spawn_sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>formation_index</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>enemy_variant_id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>level_override</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>initial_phase_id</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>required_for_victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wave_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>spawn_sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>formation_index</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>enemy_variant_id</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>level_override</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>initial_phase_id</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>required_for_victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EncounterWave.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>optional&lt;i32&gt;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>optional&lt;ref&lt;EnemyPhase.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..32</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>range=0..31</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>103</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>104</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>103</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>104</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="E14" t="n">
+        <v>108</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>107</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>107</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="E18" t="n">
+        <v>109</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>101</v>
+      </c>
+      <c r="F19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>99</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>101</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>109</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>101</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>102</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>96</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>102</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>98</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>105</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>106</v>
+      </c>
+      <c r="F31" t="n">
+        <v>24</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>111</v>
+      </c>
+      <c r="F32" t="n">
+        <v>24</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>95</v>
+      </c>
+      <c r="F33" t="n">
+        <v>24</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>106</v>
+      </c>
+      <c r="F34" t="n">
+        <v>24</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>102</v>
+      </c>
+      <c r="F35" t="n">
+        <v>24</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>110</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>30</v>
+      <c r="E37" t="n">
+        <v>97</v>
+      </c>
+      <c r="F37" t="n">
+        <v>24</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>102</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
